--- a/results/MVSE/aminer/MVSE_aminer<l01><WL>89.51.xlsx
+++ b/results/MVSE/aminer/MVSE_aminer<l01><WL>89.51.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,7 +579,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         <v>128</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>50</v>
@@ -624,20 +624,20 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>89.01000000000001</v>
+        <v>89.34</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-08_54_26', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-16_18_26', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -646,7 +646,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -665,14 +665,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WL</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
         <v>50</v>
@@ -691,20 +691,20 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>88.47</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_34_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-08_54_26', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -713,7 +713,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>50</v>
@@ -758,20 +758,20 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>87.44</v>
+        <v>88.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0.66</v>
+        <v>0.19</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_01_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_34_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -780,7 +780,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WL_0.025_0.025_0.95</t>
+          <t>WL_0_0_1</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_26_12', 'cl_mode': 'WL_0.025_0.025_0.95', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_01_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WL_0.05_0.05_0.9</t>
+          <t>WL_0.025_0.025_0.95</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_49_53', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_26_12', 'cl_mode': 'WL_0.025_0.025_0.95', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WL_0.1_0.1_0.8</t>
+          <t>WL_0.05_0.05_0.9</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -972,7 +972,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_13_05', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_49_53', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WL_0.2_0.2_0.6</t>
+          <t>WL_0.1_0.1_0.8</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_34_46', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_13_05', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WL_0.25_0.25_0.5</t>
+          <t>WL_0.2_0.2_0.6</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_57_51', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_34_46', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WL_0.33_0.33_0.33</t>
+          <t>WL_0.25_0.25_0.5</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1173,10 +1173,77 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_57_51', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>aminer</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>WL_0.33_0.33_0.33</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_59_45', 'cl_mode': 'WL_0.33_0.33_0.33', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
     </row>

--- a/results/MVSE/aminer/MVSE_aminer<l01><WL>89.51.xlsx
+++ b/results/MVSE/aminer/MVSE_aminer<l01><WL>89.51.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,7 +646,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -665,14 +665,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>128</v>
       </c>
       <c r="G4" t="n">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="H4" t="n">
         <v>50</v>
@@ -691,20 +691,20 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>89.01000000000001</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="O4" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-08_54_26', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_27-00_30_34', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 1500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -713,7 +713,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -732,14 +732,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WL</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>128</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="H5" t="n">
         <v>50</v>
@@ -758,20 +758,20 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>88.47</v>
+        <v>89.02</v>
       </c>
       <c r="N5" t="n">
         <v>0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_34_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_28-09_19_48', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 3000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -780,7 +780,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -799,14 +799,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WL</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>128</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>50</v>
@@ -825,20 +825,20 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>87.44</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="O6" t="n">
-        <v>0.66</v>
+        <v>0.22</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_01_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-08_54_26', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 200, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -847,7 +847,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H7" t="n">
         <v>50</v>
@@ -885,27 +885,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WL_0.025_0.025_0.95</t>
+          <t>WL_0_0_1</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>87.44</v>
+        <v>88.98</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>0.66</v>
+        <v>0.27</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_26_12', 'cl_mode': 'WL_0.025_0.025_0.95', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_28-09_08_04', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -940,7 +940,7 @@
         <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H8" t="n">
         <v>50</v>
@@ -952,27 +952,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>WL_0.05_0.05_0.9</t>
+          <t>WL_0_0_1</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>87.44</v>
+        <v>88.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O8" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_49_53', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_28-08_57_07', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2000, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -981,7 +981,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>50</v>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WL_0.1_0.1_0.8</t>
+          <t>WL_0_0_1</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="M9" t="n">
-        <v>87.44</v>
+        <v>88.47</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0.66</v>
+        <v>0.19</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_13_05', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_34_23', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 100, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1048,7 +1048,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WL_0.2_0.2_0.6</t>
+          <t>WL_0_0_1</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_34_46', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_01_54', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>WL_0.25_0.25_0.5</t>
+          <t>WL_0.025_0.025_0.95</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_57_51', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_26_12', 'cl_mode': 'WL_0.025_0.025_0.95', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>WL_0.33_0.33_0.33</t>
+          <t>WL_0.05_0.05_0.9</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1240,10 +1240,278 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-22_49_53', 'cl_mode': 'WL_0.05_0.05_0.9', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>aminer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>128</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WL_0.1_0.1_0.8</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_13_05', 'cl_mode': 'WL_0.1_0.1_0.8', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>aminer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>128</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WL_0.2_0.2_0.6</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_34_46', 'cl_mode': 'WL_0.2_0.2_0.6', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>aminer</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>128</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WL_0.25_0.25_0.5</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_24-23_57_51', 'cl_mode': 'WL_0.25_0.25_0.5', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MVSE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MPRW</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>aminer</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>128</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>mp_spec</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>WL_0.33_0.33_0.33</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_25-00_59_45', 'cl_mode': 'WL_0.33_0.33_0.33', 'clip_norm': 1.0, 'dataset': 'aminer', 'exp_name': 'WL', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': [['pa', 'ap'], ['pp', 'pp']], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 0, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
     </row>
